--- a/excel/example-ReverseSplitLog.xlsx
+++ b/excel/example-ReverseSplitLog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaff\Documents\Python\github\auto-rsa\main\RSAssistant\data\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaff\Documents\Python\github\orderFlowbot\main\RSAssistant\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5238BA34-CE4F-499F-B076-9B0172752DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABE2B1D-F3FD-4F70-96B4-9185C365ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20820" yWindow="1185" windowWidth="18600" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26640" yWindow="735" windowWidth="18600" windowHeight="13920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reverse Split Log" sheetId="3" r:id="rId1"/>
@@ -298,7 +298,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -326,8 +326,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -337,7 +335,12 @@
     <cellStyle name="Default Dark" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.1498764000366222"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.1498764000366222"/>
@@ -600,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33956B6D-9B83-4260-B581-B76FA865052C}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.375" customWidth="1"/>
@@ -609,9 +612,11 @@
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10">
         <f>SUM(42:42)</f>
         <v>0</v>
@@ -636,8 +641,10 @@
         <f>E2</f>
         <v>45426</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -652,8 +659,10 @@
         <v>45426</v>
       </c>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -672,304 +681,380 @@
       <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
-    </row>
-    <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>3</v>
       </c>
@@ -992,10 +1077,21 @@
         <f>SUMIF(F4:F40,"&gt;0")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G41" s="6">
+        <f>SUM(G4:G40)</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="6">
+        <f>SUMIF(H4:H40,"&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
+      <c r="B42" s="10">
+        <f>SUM(C42:K42)</f>
+        <v>0</v>
+      </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9">
         <f>D41-C41</f>
@@ -1006,11 +1102,21 @@
         <f>F41-E41</f>
         <v>0</v>
       </c>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9">
+        <f>H41-G41</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:F42">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="N/A">
+      <formula>NOT(ISERROR(SEARCH("N/A",C4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:H42">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",C4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("N/A",G4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1030,44 +1136,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>1234</v>
       </c>
       <c r="D4" s="13" t="s">
@@ -1084,7 +1190,7 @@
       <c r="B5" s="13">
         <v>1</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="13">
         <v>1234</v>
       </c>
       <c r="D5" s="13" t="s">

--- a/excel/example-ReverseSplitLog.xlsx
+++ b/excel/example-ReverseSplitLog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaff\Documents\Python\github\orderFlowbot\main\RSAssistant\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chaff\Documents\Python\github\auto-rsa\orderFlowbot\RSAssistant\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABE2B1D-F3FD-4F70-96B4-9185C365ABEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC23843-2F31-4A64-8B5F-F7EF65D9883F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26640" yWindow="735" windowWidth="18600" windowHeight="13920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37665" yWindow="735" windowWidth="18600" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reverse Split Log" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Account Names</t>
   </si>
@@ -66,9 +66,6 @@
     <t>.</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Robinhood</t>
   </si>
   <si>
@@ -94,6 +91,12 @@
   </si>
   <si>
     <t>A7</t>
+  </si>
+  <si>
+    <t>Formatting Source</t>
+  </si>
+  <si>
+    <t>Row</t>
   </si>
 </sst>
 </file>
@@ -159,7 +162,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -169,12 +172,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,7 +293,7 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -304,30 +301,32 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -617,38 +616,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10">
+      <c r="A1" s="8">
         <f>SUM(42:42)</f>
         <v>0</v>
       </c>
-      <c r="B1" s="10">
+      <c r="B1" s="8">
         <f>SUM(42:42)</f>
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="str">
-        <f>C3</f>
-        <v>RCON</v>
-      </c>
-      <c r="D1" s="12">
-        <f>C2</f>
+      <c r="C1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10">
         <v>45383</v>
       </c>
-      <c r="E1" s="11" t="str">
-        <f>E3</f>
-        <v>TIRX</v>
-      </c>
-      <c r="F1" s="12">
-        <f>E2</f>
+      <c r="E1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="10">
         <v>45426</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="1">
@@ -662,461 +657,453 @@
       <c r="G2" s="1"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3"/>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="4">
         <f>SUM(C4:C40)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="4">
         <f>SUMIF(D4:D40,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="4">
         <f>SUM(E4:E40)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="4">
         <f>SUMIF(F4:F40,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="4">
         <f>SUM(G4:G40)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="4">
         <f>SUMIF(H4:H40,"&gt;0")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8">
         <f>SUM(C42:K42)</f>
         <v>0</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9">
+      <c r="C42" s="7"/>
+      <c r="D42" s="7">
         <f>D41-C41</f>
         <v>0</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9">
+      <c r="E42" s="7"/>
+      <c r="F42" s="7">
         <f>F41-E41</f>
         <v>0</v>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9">
+      <c r="G42" s="7"/>
+      <c r="H42" s="7">
         <f>H41-G41</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C4:F42">
+  <conditionalFormatting sqref="C4:H42">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH("N/A",C4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:H42">
+  <conditionalFormatting sqref="C3:H3">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",G4)))</formula>
+      <formula>NOT(ISERROR(SEARCH("N/A",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1136,684 +1123,684 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11">
+        <v>1234</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B5" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C5" s="11">
         <v>1234</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="D5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B6" s="11">
         <v>1</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C6" s="11">
         <v>1234</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="D6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B7" s="11">
         <v>1</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C7" s="11">
         <v>1234</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="D7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="13">
-        <v>1</v>
-      </c>
-      <c r="C7" s="13">
-        <v>1234</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
+      <c r="A34" s="11"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
+      <c r="A62" s="11"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="11"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65" s="13"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="11"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="11"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="11"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
+      <c r="A85" s="11"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="14"/>
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="12"/>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="14"/>
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="12"/>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="14"/>
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="12"/>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="14"/>
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="12"/>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F90" s="14"/>
+      <c r="F90" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
